--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N50_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0002T0006Z000C1N50_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.51349139645531</v>
+        <v>2.683442351923988</v>
       </c>
       <c r="D2" t="n">
-        <v>16.23802652351582</v>
+        <v>2.638679310071321</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3076209879967919</v>
+        <v>0.04998841054947878</v>
       </c>
       <c r="F2" t="n">
-        <v>2.000348664879541</v>
+        <v>0.3250566580429255</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.12873337244889</v>
+        <v>2.783419173022945</v>
       </c>
       <c r="D3" t="n">
-        <v>20.2387238532749</v>
+        <v>3.288792626157172</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3076209879967919</v>
+        <v>0.04998841054947878</v>
       </c>
       <c r="F3" t="n">
-        <v>2.000348664879541</v>
+        <v>0.3250566580429255</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
